--- a/rtos-api-analysis/results/memory/TizenRT_memory_and_coverage_analysis.xlsx
+++ b/rtos-api-analysis/results/memory/TizenRT_memory_and_coverage_analysis.xlsx
@@ -493,7 +493,7 @@
         <v>22079</v>
       </c>
       <c r="C4" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
       <c r="D4" t="n">
         <v>0.84</v>
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1627480</v>
+        <v>1550506</v>
       </c>
       <c r="C5" t="n">
-        <v>28.58</v>
+        <v>28.04</v>
       </c>
       <c r="D5" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="6">
@@ -541,7 +541,7 @@
         <v>23333</v>
       </c>
       <c r="C7" t="n">
-        <v>5.45</v>
+        <v>5.49</v>
       </c>
       <c r="D7" t="n">
         <v>0.89</v>
@@ -573,7 +573,7 @@
         <v>3941</v>
       </c>
       <c r="C9" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="D9" t="n">
         <v>0.85</v>
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1541101</v>
+        <v>3837818</v>
       </c>
       <c r="C12" t="n">
-        <v>172.99</v>
+        <v>216.76</v>
       </c>
       <c r="D12" t="n">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="13">
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>761810</v>
+        <v>748804</v>
       </c>
       <c r="C15" t="n">
-        <v>19.22</v>
+        <v>19.19</v>
       </c>
       <c r="D15" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="16">
@@ -698,13 +698,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10794</v>
+        <v>9551</v>
       </c>
       <c r="C17" t="n">
-        <v>5.75</v>
+        <v>5.49</v>
       </c>
       <c r="D17" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="18">
@@ -717,7 +717,7 @@
         <v>2741</v>
       </c>
       <c r="C18" t="n">
-        <v>4.64</v>
+        <v>4.68</v>
       </c>
       <c r="D18" t="n">
         <v>0.58</v>
@@ -797,7 +797,7 @@
         <v>85</v>
       </c>
       <c r="C23" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="D23" t="n">
         <v>0.6899999999999999</v>
@@ -810,13 +810,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>92200</v>
+        <v>90190</v>
       </c>
       <c r="C24" t="n">
-        <v>6.91</v>
+        <v>6.98</v>
       </c>
       <c r="D24" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="25">
@@ -829,7 +829,7 @@
         <v>477</v>
       </c>
       <c r="C25" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="D25" t="n">
         <v>0.91</v>
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10564090</v>
+        <v>242844</v>
       </c>
       <c r="C31" t="n">
-        <v>555.96</v>
+        <v>20.2</v>
       </c>
       <c r="D31" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="32">
@@ -1005,7 +1005,7 @@
         <v>1582</v>
       </c>
       <c r="C36" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="D36" t="n">
         <v>0.85</v>
@@ -1021,7 +1021,7 @@
         <v>133</v>
       </c>
       <c r="C37" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -1197,7 +1197,7 @@
         <v>1303</v>
       </c>
       <c r="C48" t="n">
-        <v>7.17</v>
+        <v>7.18</v>
       </c>
       <c r="D48" t="n">
         <v>0.12</v>
@@ -1229,7 +1229,7 @@
         <v>29259</v>
       </c>
       <c r="C50" t="n">
-        <v>5.52</v>
+        <v>5.58</v>
       </c>
       <c r="D50" t="n">
         <v>0.88</v>
@@ -1242,13 +1242,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1618964</v>
+        <v>1542502</v>
       </c>
       <c r="C51" t="n">
-        <v>28.58</v>
+        <v>28.04</v>
       </c>
       <c r="D51" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="52">
@@ -1357,7 +1357,7 @@
         <v>1552</v>
       </c>
       <c r="C58" t="n">
-        <v>4.92</v>
+        <v>4.94</v>
       </c>
       <c r="D58" t="n">
         <v>0.22</v>
@@ -1405,7 +1405,7 @@
         <v>5094</v>
       </c>
       <c r="C61" t="n">
-        <v>8.699999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="D61" t="n">
         <v>0.06</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>902082</v>
+        <v>877012</v>
       </c>
       <c r="C64" t="n">
-        <v>21.16</v>
+        <v>20.97</v>
       </c>
       <c r="D64" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="65">
@@ -1517,7 +1517,7 @@
         <v>1822</v>
       </c>
       <c r="C68" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="D68" t="n">
         <v>0.52</v>
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>10132</v>
+        <v>8889</v>
       </c>
       <c r="C70" t="n">
-        <v>5.67</v>
+        <v>5.41</v>
       </c>
       <c r="D70" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="71">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2733</v>
+        <v>723</v>
       </c>
       <c r="C74" t="n">
         <v>4.4</v>
       </c>
       <c r="D74" t="n">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="75">
@@ -1757,7 +1757,7 @@
         <v>3677</v>
       </c>
       <c r="C83" t="n">
-        <v>4.78</v>
+        <v>4.86</v>
       </c>
       <c r="D83" t="n">
         <v>0.63</v>
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>14790575</v>
+        <v>4983462</v>
       </c>
       <c r="C84" t="n">
-        <v>190.45</v>
+        <v>69.06</v>
       </c>
       <c r="D84" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
@@ -1837,7 +1837,7 @@
         <v>17704</v>
       </c>
       <c r="C88" t="n">
-        <v>8.23</v>
+        <v>8.44</v>
       </c>
       <c r="D88" t="n">
         <v>0.67</v>
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>523352</v>
+        <v>521342</v>
       </c>
       <c r="C92" t="n">
-        <v>15.28</v>
+        <v>15.38</v>
       </c>
       <c r="D92" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="93">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>395512</v>
+        <v>393502</v>
       </c>
       <c r="C93" t="n">
-        <v>14.01</v>
+        <v>14.09</v>
       </c>
       <c r="D93" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="94">
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2717</v>
+        <v>707</v>
       </c>
       <c r="C94" t="n">
         <v>4.38</v>
       </c>
       <c r="D94" t="n">
-        <v>0.95</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="95">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>187807</v>
+        <v>185767</v>
       </c>
       <c r="C98" t="n">
-        <v>161.6</v>
+        <v>135.66</v>
       </c>
       <c r="D98" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="99">
@@ -2029,7 +2029,7 @@
         <v>1611</v>
       </c>
       <c r="C100" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="D100" t="n">
         <v>0.93</v>
@@ -2045,7 +2045,7 @@
         <v>24712</v>
       </c>
       <c r="C101" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="D101" t="n">
         <v>0.42</v>
@@ -2058,13 +2058,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>229549</v>
+        <v>227539</v>
       </c>
       <c r="C102" t="n">
-        <v>133.29</v>
+        <v>149.46</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="103">
@@ -2125,7 +2125,7 @@
         <v>278</v>
       </c>
       <c r="C106" t="n">
-        <v>5.91</v>
+        <v>6.01</v>
       </c>
       <c r="D106" t="n">
         <v>0.95</v>
@@ -2173,7 +2173,7 @@
         <v>82591</v>
       </c>
       <c r="C109" t="n">
-        <v>6.26</v>
+        <v>6.29</v>
       </c>
       <c r="D109" t="n">
         <v>0.95</v>
@@ -2189,7 +2189,7 @@
         <v>28738</v>
       </c>
       <c r="C110" t="n">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="D110" t="n">
         <v>0.89</v>
@@ -2218,13 +2218,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>390922</v>
+        <v>693623</v>
       </c>
       <c r="C112" t="n">
-        <v>117.41</v>
+        <v>143.25</v>
       </c>
       <c r="D112" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="113">
@@ -2298,13 +2298,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>16690</v>
+        <v>15447</v>
       </c>
       <c r="C117" t="n">
-        <v>5.79</v>
+        <v>5.52</v>
       </c>
       <c r="D117" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="118">
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>36751</v>
+        <v>35508</v>
       </c>
       <c r="C118" t="n">
-        <v>6.2</v>
+        <v>6.21</v>
       </c>
       <c r="D118" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="119">
@@ -2333,7 +2333,7 @@
         <v>15107</v>
       </c>
       <c r="C119" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
       <c r="D119" t="n">
         <v>0.88</v>
@@ -2381,7 +2381,7 @@
         <v>5300</v>
       </c>
       <c r="C122" t="n">
-        <v>7.26</v>
+        <v>7.28</v>
       </c>
       <c r="D122" t="n">
         <v>0.1</v>
@@ -2397,7 +2397,7 @@
         <v>22880</v>
       </c>
       <c r="C123" t="n">
-        <v>4.94</v>
+        <v>4.96</v>
       </c>
       <c r="D123" t="n">
         <v>0.78</v>
@@ -2426,13 +2426,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>5783351</v>
+        <v>3099081</v>
       </c>
       <c r="C125" t="n">
-        <v>94.31999999999999</v>
+        <v>54.88</v>
       </c>
       <c r="D125" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="126">
@@ -2573,7 +2573,7 @@
         <v>6236</v>
       </c>
       <c r="C134" t="n">
-        <v>6.02</v>
+        <v>6.03</v>
       </c>
       <c r="D134" t="n">
         <v>0.12</v>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>5584</v>
+        <v>3574</v>
       </c>
       <c r="C135" t="n">
         <v>4.5</v>
       </c>
       <c r="D135" t="n">
-        <v>0.97</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="136">
@@ -2685,7 +2685,7 @@
         <v>2528</v>
       </c>
       <c r="C141" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="D141" t="n">
         <v>0.89</v>
@@ -2781,7 +2781,7 @@
         <v>66</v>
       </c>
       <c r="C147" t="n">
-        <v>4.95</v>
+        <v>4.99</v>
       </c>
       <c r="D147" t="n">
         <v>0.05</v>
@@ -2877,7 +2877,7 @@
         <v>3058</v>
       </c>
       <c r="C153" t="n">
-        <v>5.96</v>
+        <v>5.97</v>
       </c>
       <c r="D153" t="n">
         <v>0.11</v>
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>918478</v>
+        <v>769952</v>
       </c>
       <c r="C155" t="n">
-        <v>21.93</v>
+        <v>19.73</v>
       </c>
       <c r="D155" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="156">
@@ -2938,13 +2938,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>127752</v>
+        <v>122812</v>
       </c>
       <c r="C157" t="n">
-        <v>110.18</v>
+        <v>118.96</v>
       </c>
       <c r="D157" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="158">
@@ -2989,7 +2989,7 @@
         <v>62322</v>
       </c>
       <c r="C160" t="n">
-        <v>5.92</v>
+        <v>5.94</v>
       </c>
       <c r="D160" t="n">
         <v>0.97</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2354.74</v>
+        <v>1723.7</v>
       </c>
       <c r="B2" t="n">
-        <v>14.6257</v>
+        <v>10.7062</v>
       </c>
       <c r="C2" t="n">
-        <v>555.96</v>
+        <v>216.76</v>
       </c>
       <c r="D2" t="n">
         <v>4.05</v>
       </c>
       <c r="E2" t="n">
-        <v>51.6066</v>
+        <v>27.22</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7443</v>
+        <v>0.7316</v>
       </c>
       <c r="G2" t="n">
         <v>0.4472</v>

--- a/rtos-api-analysis/results/memory/TizenRT_memory_and_coverage_analysis.xlsx
+++ b/rtos-api-analysis/results/memory/TizenRT_memory_and_coverage_analysis.xlsx
@@ -458,13 +458,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94</v>
+        <v>3354</v>
       </c>
       <c r="C2" t="n">
-        <v>7.24</v>
+        <v>7.69</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="3">
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>618</v>
+        <v>815</v>
       </c>
       <c r="C3" t="n">
-        <v>5.25</v>
+        <v>5.26</v>
       </c>
       <c r="D3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22079</v>
+        <v>47643</v>
       </c>
       <c r="C4" t="n">
-        <v>5.25</v>
+        <v>5.52</v>
       </c>
       <c r="D4" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1550506</v>
+        <v>50363</v>
       </c>
       <c r="C5" t="n">
-        <v>28.04</v>
+        <v>10.48</v>
       </c>
       <c r="D5" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="6">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23333</v>
+        <v>24159</v>
       </c>
       <c r="C7" t="n">
-        <v>5.49</v>
+        <v>5.44</v>
       </c>
       <c r="D7" t="n">
         <v>0.89</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3941</v>
+        <v>3943</v>
       </c>
       <c r="C9" t="n">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="10">
@@ -589,7 +589,7 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="D10" t="n">
         <v>0.88</v>
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>1433011</v>
       </c>
       <c r="C11" t="n">
-        <v>5.35</v>
+        <v>35.27</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="12">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3837818</v>
+        <v>12454623</v>
       </c>
       <c r="C12" t="n">
-        <v>216.76</v>
+        <v>468.73</v>
       </c>
       <c r="D12" t="n">
         <v>0.48</v>
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>748804</v>
+        <v>1280907</v>
       </c>
       <c r="C15" t="n">
-        <v>19.19</v>
+        <v>25.98</v>
       </c>
       <c r="D15" t="n">
         <v>0.38</v>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9551</v>
+        <v>10370</v>
       </c>
       <c r="C17" t="n">
-        <v>5.49</v>
+        <v>5.47</v>
       </c>
       <c r="D17" t="n">
         <v>0.44</v>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2741</v>
+        <v>2854</v>
       </c>
       <c r="C18" t="n">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
       <c r="D18" t="n">
         <v>0.58</v>
@@ -797,7 +797,7 @@
         <v>85</v>
       </c>
       <c r="C23" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="D23" t="n">
         <v>0.6899999999999999</v>
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>90190</v>
+        <v>103443</v>
       </c>
       <c r="C24" t="n">
-        <v>6.98</v>
+        <v>7.19</v>
       </c>
       <c r="D24" t="n">
         <v>0.51</v>
@@ -829,10 +829,10 @@
         <v>477</v>
       </c>
       <c r="C25" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="D25" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="26">
@@ -877,7 +877,7 @@
         <v>21</v>
       </c>
       <c r="C28" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="D28" t="n">
         <v>0.91</v>
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C29" t="n">
         <v>4.12</v>
       </c>
       <c r="D29" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="30">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>242844</v>
+        <v>7002094</v>
       </c>
       <c r="C31" t="n">
-        <v>20.2</v>
+        <v>650.2</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="32">
@@ -957,7 +957,7 @@
         <v>2143</v>
       </c>
       <c r="C33" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="D33" t="n">
         <v>0.9</v>
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1582</v>
+        <v>1912</v>
       </c>
       <c r="C36" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="D36" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="37">
@@ -1021,7 +1021,7 @@
         <v>133</v>
       </c>
       <c r="C37" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -1104,7 +1104,7 @@
         <v>4.23</v>
       </c>
       <c r="D42" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="43">
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>234</v>
+        <v>299</v>
       </c>
       <c r="C43" t="n">
         <v>4.22</v>
       </c>
       <c r="D43" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="44">
@@ -1181,7 +1181,7 @@
         <v>20</v>
       </c>
       <c r="C47" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1303</v>
+        <v>1320</v>
       </c>
       <c r="C48" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="D48" t="n">
         <v>0.12</v>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29259</v>
+        <v>29809</v>
       </c>
       <c r="C50" t="n">
-        <v>5.58</v>
+        <v>5.52</v>
       </c>
       <c r="D50" t="n">
         <v>0.88</v>
@@ -1242,13 +1242,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1542502</v>
+        <v>52297</v>
       </c>
       <c r="C51" t="n">
-        <v>28.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="52">
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
       <c r="C55" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -1354,13 +1354,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1552</v>
+        <v>20811</v>
       </c>
       <c r="C58" t="n">
-        <v>4.94</v>
+        <v>5.24</v>
       </c>
       <c r="D58" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="59">
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C60" t="n">
         <v>4.08</v>
       </c>
       <c r="D60" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>5094</v>
+        <v>6189</v>
       </c>
       <c r="C61" t="n">
-        <v>8.710000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D61" t="n">
         <v>0.06</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>877012</v>
+        <v>1507023</v>
       </c>
       <c r="C64" t="n">
-        <v>20.97</v>
+        <v>29.26</v>
       </c>
       <c r="D64" t="n">
         <v>0.39</v>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1822</v>
+        <v>2378</v>
       </c>
       <c r="C68" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="D68" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="69">
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8889</v>
+        <v>9708</v>
       </c>
       <c r="C70" t="n">
-        <v>5.41</v>
+        <v>5.39</v>
       </c>
       <c r="D70" t="n">
         <v>0.42</v>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6715</v>
+        <v>15204</v>
       </c>
       <c r="C71" t="n">
-        <v>6.03</v>
+        <v>6.13</v>
       </c>
       <c r="D71" t="n">
         <v>0.13</v>
@@ -1613,7 +1613,7 @@
         <v>723</v>
       </c>
       <c r="C74" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="D74" t="n">
         <v>0.64</v>
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>298</v>
+        <v>357010</v>
       </c>
       <c r="C81" t="n">
-        <v>5.11</v>
+        <v>9.1</v>
       </c>
       <c r="D81" t="n">
-        <v>0.12</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="82">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3677</v>
+        <v>3687</v>
       </c>
       <c r="C83" t="n">
-        <v>4.86</v>
+        <v>4.79</v>
       </c>
       <c r="D83" t="n">
         <v>0.63</v>
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4983462</v>
+        <v>567105</v>
       </c>
       <c r="C84" t="n">
-        <v>69.06</v>
+        <v>13.75</v>
       </c>
       <c r="D84" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="85">
@@ -1792,7 +1792,7 @@
         <v>4.08</v>
       </c>
       <c r="D85" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="86">
@@ -1805,7 +1805,7 @@
         <v>1638</v>
       </c>
       <c r="C86" t="n">
-        <v>8.699999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="D86" t="n">
         <v>0.04</v>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>17704</v>
+        <v>17710</v>
       </c>
       <c r="C88" t="n">
-        <v>8.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D88" t="n">
         <v>0.67</v>
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>521342</v>
+        <v>679402</v>
       </c>
       <c r="C92" t="n">
-        <v>15.38</v>
+        <v>16.96</v>
       </c>
       <c r="D92" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="93">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>393502</v>
+        <v>531402</v>
       </c>
       <c r="C93" t="n">
-        <v>14.09</v>
+        <v>15.83</v>
       </c>
       <c r="D93" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="94">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C94" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="D94" t="n">
         <v>0.62</v>
@@ -1962,13 +1962,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>197</v>
+        <v>344</v>
       </c>
       <c r="C96" t="n">
         <v>4.22</v>
       </c>
       <c r="D96" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="97">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>185767</v>
+        <v>4861868</v>
       </c>
       <c r="C98" t="n">
-        <v>135.66</v>
+        <v>371.31</v>
       </c>
       <c r="D98" t="n">
         <v>0.17</v>
@@ -2029,7 +2029,7 @@
         <v>1611</v>
       </c>
       <c r="C100" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="D100" t="n">
         <v>0.93</v>
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>24712</v>
+        <v>191008</v>
       </c>
       <c r="C101" t="n">
-        <v>5.78</v>
+        <v>7.47</v>
       </c>
       <c r="D101" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="102">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>227539</v>
+        <v>7816619</v>
       </c>
       <c r="C102" t="n">
-        <v>149.46</v>
+        <v>425.13</v>
       </c>
       <c r="D102" t="n">
         <v>0.19</v>
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>278</v>
+        <v>326</v>
       </c>
       <c r="C106" t="n">
-        <v>6.01</v>
+        <v>6.03</v>
       </c>
       <c r="D106" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="107">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>82591</v>
+        <v>116587</v>
       </c>
       <c r="C109" t="n">
-        <v>6.29</v>
+        <v>6.7</v>
       </c>
       <c r="D109" t="n">
         <v>0.95</v>
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>28738</v>
+        <v>29564</v>
       </c>
       <c r="C110" t="n">
-        <v>5.61</v>
+        <v>5.56</v>
       </c>
       <c r="D110" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="111">
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>693623</v>
+        <v>7895101</v>
       </c>
       <c r="C112" t="n">
-        <v>143.25</v>
+        <v>333.63</v>
       </c>
       <c r="D112" t="n">
         <v>0.47</v>
@@ -2234,13 +2234,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>65</v>
+        <v>28445</v>
       </c>
       <c r="C113" t="n">
-        <v>5.91</v>
+        <v>6.79</v>
       </c>
       <c r="D113" t="n">
-        <v>0.02</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="114">
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>15447</v>
+        <v>15971</v>
       </c>
       <c r="C117" t="n">
-        <v>5.52</v>
+        <v>5.51</v>
       </c>
       <c r="D117" t="n">
         <v>0.44</v>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>35508</v>
+        <v>39923</v>
       </c>
       <c r="C118" t="n">
-        <v>6.21</v>
+        <v>6.25</v>
       </c>
       <c r="D118" t="n">
         <v>0.48</v>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15107</v>
+        <v>15381</v>
       </c>
       <c r="C119" t="n">
-        <v>5.3</v>
+        <v>5.26</v>
       </c>
       <c r="D119" t="n">
         <v>0.88</v>
@@ -2378,13 +2378,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5300</v>
+        <v>45992</v>
       </c>
       <c r="C122" t="n">
-        <v>7.28</v>
+        <v>10.26</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="123">
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>22880</v>
+        <v>30005</v>
       </c>
       <c r="C123" t="n">
-        <v>4.96</v>
+        <v>4.97</v>
       </c>
       <c r="D123" t="n">
         <v>0.78</v>
@@ -2413,7 +2413,7 @@
         <v>20</v>
       </c>
       <c r="C124" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="D124" t="n">
         <v>1</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3099081</v>
+        <v>4991852</v>
       </c>
       <c r="C125" t="n">
-        <v>54.88</v>
+        <v>80.42</v>
       </c>
       <c r="D125" t="n">
         <v>0.49</v>
@@ -2557,7 +2557,7 @@
         <v>617</v>
       </c>
       <c r="C133" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="D133" t="n">
         <v>0.89</v>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>6236</v>
+        <v>13925</v>
       </c>
       <c r="C134" t="n">
-        <v>6.03</v>
+        <v>6.12</v>
       </c>
       <c r="D134" t="n">
         <v>0.12</v>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3574</v>
+        <v>3578</v>
       </c>
       <c r="C135" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="D135" t="n">
         <v>0.74</v>
@@ -2634,13 +2634,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>72</v>
+        <v>67006</v>
       </c>
       <c r="C138" t="n">
-        <v>4.96</v>
+        <v>5.97</v>
       </c>
       <c r="D138" t="n">
-        <v>0.05</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="139">
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>89</v>
+        <v>39221</v>
       </c>
       <c r="C139" t="n">
-        <v>7.34</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="D139" t="n">
-        <v>0.02</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="140">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2528</v>
+        <v>4847</v>
       </c>
       <c r="C141" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="D141" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="142">
@@ -2765,7 +2765,7 @@
         <v>1333</v>
       </c>
       <c r="C146" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="D146" t="n">
         <v>0.79</v>
@@ -2778,13 +2778,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>66</v>
+        <v>63723</v>
       </c>
       <c r="C147" t="n">
-        <v>4.99</v>
+        <v>5.97</v>
       </c>
       <c r="D147" t="n">
-        <v>0.05</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="148">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3058</v>
+        <v>3432</v>
       </c>
       <c r="C153" t="n">
-        <v>5.97</v>
+        <v>5.96</v>
       </c>
       <c r="D153" t="n">
         <v>0.11</v>
@@ -2890,13 +2890,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C154" t="n">
         <v>4.11</v>
       </c>
       <c r="D154" t="n">
-        <v>0.62</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="155">
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>769952</v>
+        <v>1302519</v>
       </c>
       <c r="C155" t="n">
-        <v>19.73</v>
+        <v>26.44</v>
       </c>
       <c r="D155" t="n">
         <v>0.41</v>
@@ -2928,7 +2928,7 @@
         <v>4.08</v>
       </c>
       <c r="D156" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="157">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>122812</v>
+        <v>195724</v>
       </c>
       <c r="C157" t="n">
-        <v>118.96</v>
+        <v>100.22</v>
       </c>
       <c r="D157" t="n">
         <v>0.39</v>
@@ -2986,13 +2986,13 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>62322</v>
+        <v>90862</v>
       </c>
       <c r="C160" t="n">
-        <v>5.94</v>
+        <v>6.31</v>
       </c>
       <c r="D160" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="161">
@@ -3095,28 +3095,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1723.7</v>
+        <v>3291.83</v>
       </c>
       <c r="B2" t="n">
-        <v>10.7062</v>
+        <v>20.4461</v>
       </c>
       <c r="C2" t="n">
-        <v>216.76</v>
+        <v>650.2</v>
       </c>
       <c r="D2" t="n">
         <v>4.05</v>
       </c>
       <c r="E2" t="n">
-        <v>27.22</v>
+        <v>80.20959999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7316</v>
+        <v>0.761</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4472</v>
+        <v>0.4534</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0683</v>
+        <v>0.0435</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
